--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>06/11 00:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>200</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>06/11 02:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>200</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>06/11 03:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>200</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>06/11 03:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>200</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>06/11 00:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>200</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>05/11 03:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>200</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>05/11 02:30</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>200</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>05/11 03:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>150</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>09/11 17:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>125</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>06/11 16:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>101</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>05/11 14:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>101</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>06/11 16:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>101</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>06/11 16:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>101</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>06/11 16:10</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>90</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>06/11 16:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>101</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>05/11 09:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>101</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>05/11 03:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>100</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>08/11 15:30</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>60</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>05/11 09:15</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>90</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>06/11 16:30</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>90</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>07/11 16:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>55</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>09/11 15:30</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>55</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>05/11 14:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>90</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>09/11 15:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>60</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45966.0740793306</v>
+        <v>45966.0740793287</v>
       </c>
     </row>
     <row r="26">
@@ -1585,23 +1537,201 @@
           <t>09/11 13:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>55</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+27,6%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45966.0740793287</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sparta Prague – LiberecRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>09/11 17:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+101%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45966.13438540848</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FK Oleksan</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FK Oleksandria – FC Polissya ZhytomyrUPL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>09/11 11:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>55.00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>+27,6%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>45966.0740793306</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+24,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45966.13438540848</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 2.52e équipe | Differdang</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Differdange 03 – Rodange 91Luxembourg - Luxembourg Division 1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>05/11 18:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+20,7%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45966.13438540848</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | FC Unirea </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FC Unirea 2004 Slobozia – CFR ClujLiga 1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>09/11 12:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+14,2%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45966.13438540848</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>09/11 17:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>125</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45966.13438540848</v>
+        <v>45966.13438540509</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>09/11 11:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>55</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45966.13438540848</v>
+        <v>45966.13438540509</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>05/11 18:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>40</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45966.13438540848</v>
+        <v>45966.13438540509</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>09/11 12:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>55</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,97 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45966.13438540848</v>
+        <v>45966.13438540509</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 12.5 - tirs1re équipe | Sporting B</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Sporting Braga – GenkEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Moins que 12.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>06/11 20:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>38,3%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+11,1%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45966.18524590264</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 14.5 - tirs2e équipe | Pafos FC –</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Pafos FC – VillarrealLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 14.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>05/11 17:45</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>67,6%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+8,14%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45966.18524590264</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>06/11 20:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F31" t="n">
+        <v>2.9</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45966.18524590264</v>
+        <v>45966.18524590278</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>05/11 17:45</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="F32" t="n">
+        <v>1.6</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,97 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45966.18524590264</v>
+        <v>45966.18524590278</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Once Calda</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Once Caldas – AD Pasto385076e7 Primera A</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>09/11 19:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+19,8%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45966.22393847823</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | Pescara – </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Pescara – AC MonzaSerie B</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>09/11 16:15</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+18,2%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45966.22393847823</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>09/11 19:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>55</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45966.22393847823</v>
+        <v>45966.2239384838</v>
       </c>
     </row>
     <row r="34">
@@ -1883,23 +1881,66 @@
           <t>09/11 16:15</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="n">
+        <v>55</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+18,2%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45966.2239384838</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Independie</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia – Argentinos JuniorsCoupe d'Argentine</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>06/11 00:10</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>55.00</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>+18,2%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>45966.22393847823</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+22,1%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45966.27342140501</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>06/11 00:10</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>55</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,52 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45966.27342140501</v>
+        <v>45966.27342140046</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Stan Wawri</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Stan Wawrinka – Lorenzo MusettiATP - Athènes</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>05/11 16:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>42,5%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+27,5%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45966.3068162654</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -1967,10 +1967,8 @@
           <t>05/11 16:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>3</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45966.3068162654</v>
+        <v>45966.30681626157</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1984,6 +1984,96 @@
         <v>45966.30681626157</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | Washington</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Washington Capitals – St. Louis BluesUSA - NHL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>06/11 00:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+67,7%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45966.39276121509</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 2.52e équipe | Inter Mila</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Inter Milan – Kairat AlmatyEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>05/11 20:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>85.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+65,8%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45966.39276121509</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>06/11 00:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>101</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45966.39276121509</v>
+        <v>45966.39276121528</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>05/11 20:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>85.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>85</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,52 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45966.39276121509</v>
+        <v>45966.39276121528</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 18.5 - tirs1re équipe | Inter Mila</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Inter Milan – KairatEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Moins que 18.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>05/11 20:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>43,7%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+31,0%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45966.43430725891</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,10 +2096,8 @@
           <t>05/11 20:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>3</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,97 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45966.43430725891</v>
+        <v>45966.43430725695</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 8.5 - tirs2e équipe | Inter Mila</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Inter Milan – Kairat AlmatyEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>05/11 20:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>42,6%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+21,3%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45966.47223849021</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | CA Tembeta</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CA Tembetary Ypane – Nacional AsuncionPrimera Division</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>10/11 22:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+19,7%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45966.47223849021</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>05/11 20:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F40" t="n">
+        <v>2.85</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45966.47223849021</v>
+        <v>45966.47223849537</v>
       </c>
     </row>
     <row r="41">
@@ -2184,10 +2182,8 @@
           <t>10/11 22:30</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>50</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2200,7 +2196,52 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45966.47223849021</v>
+        <v>45966.47223849537</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football | 2 | FC Differd</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FC Differdange 03 – FC RodangeLuxembourg - Division Nationale</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>05/11 18:30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+26,2%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45966.53262311644</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,10 +2225,8 @@
           <t>05/11 18:30</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>30.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>30</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,52 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45966.53262311644</v>
+        <v>45966.53262311342</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 8.5 - tirs2e équipe | Inter Mila</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Inter Milan – Kairat AlmatyLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>05/11 20:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>44,9%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+23,5%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45966.56535034156</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -2268,10 +2268,8 @@
           <t>05/11 20:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F43" t="n">
+        <v>2.75</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2284,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45966.56535034156</v>
+        <v>45966.56535034722</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2285,6 +2285,141 @@
         <v>45966.56535034722</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Chaves – F</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Chaves – FC Porto BPortugal, Segunda Liga</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>08/11 18:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+28,6%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45966.6409421732</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X1re période[race to 25 regular time] | Miami Heat</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Miami Heat – Denver NuggetsNBA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>X1re période[race to 25 regular time]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>06/11 02:10</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+23,7%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45966.6409421732</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Dinamo Buc</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Dinamo Bucarest – FK Csikszereda Miercurea CiucLiga 1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>08/11 15:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+21,7%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45966.6409421732</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,10 +2311,8 @@
           <t>08/11 18:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>55</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45966.6409421732</v>
+        <v>45966.64094217592</v>
       </c>
     </row>
     <row r="45">
@@ -2356,10 +2354,8 @@
           <t>06/11 02:10</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>40</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2372,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45966.6409421732</v>
+        <v>45966.64094217592</v>
       </c>
     </row>
     <row r="46">
@@ -2401,10 +2397,8 @@
           <t>08/11 15:30</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>60</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2417,7 +2411,367 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45966.6409421732</v>
+        <v>45966.64094217592</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Boston Bru</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Boston Bruins – Ottawa SenatorsNHL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>07/11 00:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+158%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45966.68747928496</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | New Jersey</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>New Jersey Devils – Montreal CanadiensNHL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>07/11 00:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+158%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45966.68747928496</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Carolina H</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Carolina Hurricanes – Minnesota WildNHL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>07/11 00:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+155%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45966.68747928496</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Dallas Sta</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Dallas Stars – Anaheim DucksNHL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>07/11 01:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+154%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45966.68747928496</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Pittsburgh</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Pittsburgh Penguins – Washington CapitalsNHL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>07/11 00:30</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+154%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45966.68747928496</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Buffalo Sa</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Buffalo Sabres – St. Louis BluesNHL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>07/11 00:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+153%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45966.68747928496</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Nashville </t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Nashville Predators – Philadelphia FlyersNHL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>07/11 01:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1,30%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+128%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45966.68747928496</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | Neftekhimi</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Neftekhimik Nijnekamsk – Salavat Yulaev UFARussia - KHL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>07/11 16:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+61,7%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45966.68747928496</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>07/11 00:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>200</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45966.68747928496</v>
+        <v>45966.68747928241</v>
       </c>
     </row>
     <row r="48">
@@ -2485,10 +2483,8 @@
           <t>07/11 00:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>200</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2501,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45966.68747928496</v>
+        <v>45966.68747928241</v>
       </c>
     </row>
     <row r="49">
@@ -2530,10 +2526,8 @@
           <t>07/11 00:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>200</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2546,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45966.68747928496</v>
+        <v>45966.68747928241</v>
       </c>
     </row>
     <row r="50">
@@ -2575,10 +2569,8 @@
           <t>07/11 01:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>200</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2591,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45966.68747928496</v>
+        <v>45966.68747928241</v>
       </c>
     </row>
     <row r="51">
@@ -2620,10 +2612,8 @@
           <t>07/11 00:30</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>200</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2636,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45966.68747928496</v>
+        <v>45966.68747928241</v>
       </c>
     </row>
     <row r="52">
@@ -2665,10 +2655,8 @@
           <t>07/11 00:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>200</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2681,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45966.68747928496</v>
+        <v>45966.68747928241</v>
       </c>
     </row>
     <row r="53">
@@ -2710,10 +2698,8 @@
           <t>07/11 01:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>175</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2726,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45966.68747928496</v>
+        <v>45966.68747928241</v>
       </c>
     </row>
     <row r="54">
@@ -2755,10 +2741,8 @@
           <t>07/11 16:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>101</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2771,7 +2755,142 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45966.68747928496</v>
+        <v>45966.68747928241</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Vitkovi</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HC Vitkovice – Ceske BudejoviceExtraliga</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>12/11 16:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+76,4%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45966.72284895284</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PMU(FR)Hockey | X [№ 2 regular time] | Calgary Fl</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PMU(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Calgary Flames – Columbus Blue JacketsHockey US. NHL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>X [№ 2 regular time]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>06/11 02:40</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+50,2%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45966.72284895284</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Bili Tygri</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Bili Tygri Liberec – HC OlomoucExtraliga</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>12/11 17:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>80.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+44,5%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45966.72284895284</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,10 +2784,8 @@
           <t>12/11 16:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>100</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2800,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45966.72284895284</v>
+        <v>45966.72284895834</v>
       </c>
     </row>
     <row r="56">
@@ -2829,10 +2827,8 @@
           <t>06/11 02:40</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>40</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2845,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45966.72284895284</v>
+        <v>45966.72284895834</v>
       </c>
     </row>
     <row r="57">
@@ -2874,10 +2870,8 @@
           <t>12/11 17:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>80.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>80</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2890,7 +2884,142 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45966.72284895284</v>
+        <v>45966.72284895834</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Twk Inn</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>HC Twk Innsbruck Die Haie – Pioneers VorarlbergICE</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>12/11 18:15</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+215%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45966.77223184374</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Fehervar A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Fehervar AV19 – BolzanoAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>12/11 18:15</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+174%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45966.77223184374</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | KAC Klagen</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>KAC Klagenfurt – Black Wings LinzICE</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>12/11 18:15</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+141%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45966.77223184374</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,10 +2913,8 @@
           <t>12/11 18:15</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>200</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2929,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45966.77223184374</v>
+        <v>45966.77223184028</v>
       </c>
     </row>
     <row r="59">
@@ -2958,10 +2956,8 @@
           <t>12/11 18:15</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>150</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2974,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45966.77223184374</v>
+        <v>45966.77223184028</v>
       </c>
     </row>
     <row r="60">
@@ -3003,23 +2999,201 @@
           <t>12/11 18:15</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" t="n">
+        <v>140</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+141%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45966.77223184028</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | HC Pustert</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>HC Pustertal – Olimpija LjubljanaAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>12/11 18:45</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>225.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+254%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45966.80481703619</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Fehervar A</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Fehervar AV19 – BolzanoICE</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>12/11 18:15</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+168%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45966.80481703619</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | KAC – Blac</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>KAC – Black Wings LinzAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>12/11 18:15</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>+141%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>45966.77223184374</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+145%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45966.80481703619</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Vitkovice </t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Vitkovice – Ceske BudejoviceRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>12/11 16:30</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>99.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1,80%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+78,0%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45966.80481703619</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,10 +3042,8 @@
           <t>12/11 18:45</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>225</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45966.80481703619</v>
+        <v>45966.80481703704</v>
       </c>
     </row>
     <row r="62">
@@ -3087,10 +3085,8 @@
           <t>12/11 18:15</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>150</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3103,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45966.80481703619</v>
+        <v>45966.80481703704</v>
       </c>
     </row>
     <row r="63">
@@ -3132,10 +3128,8 @@
           <t>12/11 18:15</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>140</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3148,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45966.80481703619</v>
+        <v>45966.80481703704</v>
       </c>
     </row>
     <row r="64">
@@ -3177,10 +3171,8 @@
           <t>12/11 16:30</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>99.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>99</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3193,7 +3185,52 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45966.80481703619</v>
+        <v>45966.80481703704</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Innsbruck </t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Innsbruck Die Haie – Pioneers VorarlbergAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>12/11 18:15</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+221%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45966.85897863237</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3214,23 +3214,66 @@
           <t>12/11 18:15</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" t="n">
+        <v>200</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+221%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45966.85897863426</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Pustertal </t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Pustertal Wolfe – Olimpija LjubljanaICE</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>12/11 18:45</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>200.00</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>1,60%</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>+221%</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>45966.85897863237</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+209%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45966.88941368676</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-05.xlsx
+++ b/data/valuebets_database_2025-11-05.xlsx
@@ -3257,10 +3257,8 @@
           <t>12/11 18:45</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>200</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3273,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45966.88941368676</v>
+        <v>45966.88941369213</v>
       </c>
     </row>
   </sheetData>
